--- a/data/DATASET_PROCESSED.xlsx
+++ b/data/DATASET_PROCESSED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02f46a889e67c377/Documents/UNS/SEM 4/Kecerdasan Buatan (AI)/TUBES AI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_933EF97ACB23767B3972C5B96778DCB4F6C0CEA0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542722BC-837A-4CA0-9D74-FBF55B564E4B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_933EF97ACB23767B3972C5B96778DCB4F6C0CEA0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E60A9FB3-AA05-4A13-AEF2-1DDEEF20B714}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="11">
   <si>
     <t>TANGGAL</t>
   </si>
@@ -56,12 +56,6 @@
     <t>BIS/TRUCK BARANG</t>
   </si>
   <si>
-    <t>Unnamed: 10</t>
-  </si>
-  <si>
-    <t>Unnamed: 11</t>
-  </si>
-  <si>
     <t/>
   </si>
 </sst>
@@ -70,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -103,7 +97,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -119,6 +113,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,6 +410,7 @@
     <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.53125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -445,12 +444,6 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
@@ -804,7 +797,7 @@
         <v>27783</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
@@ -14928,6 +14921,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.53125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -18920,6 +18918,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -26170,6 +26171,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.53125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -27192,6 +27198,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
